--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130207870</v>
+        <v>130192475</v>
       </c>
       <c r="B2" t="n">
         <v>56931</v>
@@ -703,29 +703,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555987</v>
+        <v>556371</v>
       </c>
       <c r="R2" t="n">
-        <v>6440734</v>
+        <v>6440485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,19 +768,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192475</v>
+        <v>130206069</v>
       </c>
       <c r="B3" t="n">
         <v>56931</v>
@@ -827,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556371</v>
+        <v>556351</v>
       </c>
       <c r="R3" t="n">
-        <v>6440485</v>
+        <v>6440550</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,54 +873,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206069</v>
+        <v>130205932</v>
       </c>
       <c r="B4" t="n">
-        <v>56931</v>
+        <v>79714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556351</v>
+        <v>555963</v>
       </c>
       <c r="R4" t="n">
-        <v>6440550</v>
+        <v>6440548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -987,14 +979,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130205932</v>
+        <v>130206032</v>
       </c>
       <c r="B5" t="n">
         <v>79714</v>
@@ -1032,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555963</v>
+        <v>556137</v>
       </c>
       <c r="R5" t="n">
-        <v>6440548</v>
+        <v>6440697</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,44 +1080,50 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206032</v>
+        <v>130192966</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1133,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556137</v>
+        <v>556440</v>
       </c>
       <c r="R6" t="n">
-        <v>6440697</v>
+        <v>6440510</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,53 +1182,52 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130192966</v>
+        <v>130206062</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1240,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556440</v>
+        <v>556289</v>
       </c>
       <c r="R7" t="n">
-        <v>6440510</v>
+        <v>6440643</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,72 +1281,75 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130206062</v>
+        <v>130207870</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>56931</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556289</v>
+        <v>555987</v>
       </c>
       <c r="R8" t="n">
-        <v>6440643</v>
+        <v>6440734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,12 +1396,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130193214</v>
+        <v>130206066</v>
       </c>
       <c r="B19" t="n">
         <v>79714</v>
@@ -2447,16 +2447,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556550</v>
+        <v>556348</v>
       </c>
       <c r="R19" t="n">
-        <v>6440532</v>
+        <v>6440509</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,28 +2500,29 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130206066</v>
+        <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>91660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,37 +2530,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556348</v>
+        <v>556081</v>
       </c>
       <c r="R20" t="n">
-        <v>6440509</v>
+        <v>6440690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,29 +2598,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130184275</v>
+        <v>130188670</v>
       </c>
       <c r="B21" t="n">
-        <v>91660</v>
+        <v>79714</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556081</v>
+        <v>556335</v>
       </c>
       <c r="R21" t="n">
-        <v>6440690</v>
+        <v>6440570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130188670</v>
+        <v>130186120</v>
       </c>
       <c r="B22" t="n">
         <v>79714</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556335</v>
+        <v>556179</v>
       </c>
       <c r="R22" t="n">
-        <v>6440570</v>
+        <v>6440716</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,45 +2810,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130186120</v>
+        <v>130191022</v>
       </c>
       <c r="B23" t="n">
-        <v>79714</v>
+        <v>56931</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556179</v>
+        <v>556359</v>
       </c>
       <c r="R23" t="n">
-        <v>6440716</v>
+        <v>6440535</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2907,10 +2915,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130191022</v>
+        <v>130188529</v>
       </c>
       <c r="B24" t="n">
-        <v>56931</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,29 +2926,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2950,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556359</v>
+        <v>556326</v>
       </c>
       <c r="R24" t="n">
-        <v>6440535</v>
+        <v>6440589</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,6 +3003,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3012,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130188529</v>
+        <v>130181235</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>92921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3023,43 +3033,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556326</v>
+        <v>555982</v>
       </c>
       <c r="R25" t="n">
-        <v>6440589</v>
+        <v>6440530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,7 +3101,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3119,7 +3119,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130181235</v>
+        <v>130206076</v>
       </c>
       <c r="B26" t="n">
         <v>92921</v>
@@ -3148,16 +3148,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>555982</v>
+        <v>556535</v>
       </c>
       <c r="R26" t="n">
-        <v>6440530</v>
+        <v>6440485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3198,55 +3201,61 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206076</v>
+        <v>130206002</v>
       </c>
       <c r="B27" t="n">
-        <v>92921</v>
+        <v>57738</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3254,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556535</v>
+        <v>556108</v>
       </c>
       <c r="R27" t="n">
-        <v>6440485</v>
+        <v>6440698</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,7 +3307,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3317,7 +3325,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130206002</v>
+        <v>130205958</v>
       </c>
       <c r="B28" t="n">
         <v>57738</v>
@@ -3360,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556108</v>
+        <v>556008</v>
       </c>
       <c r="R28" t="n">
-        <v>6440698</v>
+        <v>6440596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3415,60 +3423,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130205958</v>
+        <v>130184293</v>
       </c>
       <c r="B29" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556008</v>
+        <v>556081</v>
       </c>
       <c r="R29" t="n">
-        <v>6440596</v>
+        <v>6440690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,22 +3515,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130184293</v>
+        <v>130206072</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>96320</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3538,34 +3538,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>2170</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556081</v>
+        <v>556413</v>
       </c>
       <c r="R30" t="n">
-        <v>6440690</v>
+        <v>6440503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,67 +3610,64 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130206072</v>
+        <v>130181118</v>
       </c>
       <c r="B31" t="n">
-        <v>96320</v>
+        <v>79714</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556413</v>
+        <v>555982</v>
       </c>
       <c r="R31" t="n">
-        <v>6440503</v>
+        <v>6440530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,29 +3708,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130181118</v>
+        <v>130191846</v>
       </c>
       <c r="B32" t="n">
-        <v>79714</v>
+        <v>78761</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3761,10 +3761,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>555982</v>
+        <v>556374</v>
       </c>
       <c r="R32" t="n">
-        <v>6440530</v>
+        <v>6440510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3823,10 +3823,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B33" t="n">
-        <v>78761</v>
+        <v>79714</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3834,34 +3834,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R33" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3902,55 +3905,61 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130206052</v>
+        <v>130193838</v>
       </c>
       <c r="B34" t="n">
-        <v>79714</v>
+        <v>56931</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3958,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556177</v>
+        <v>556003</v>
       </c>
       <c r="R34" t="n">
-        <v>6440700</v>
+        <v>6440837</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,26 +4011,25 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130193838</v>
+        <v>130193547</v>
       </c>
       <c r="B35" t="n">
         <v>56931</v>
@@ -4054,7 +4062,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4064,10 +4072,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556003</v>
+        <v>556301</v>
       </c>
       <c r="R35" t="n">
-        <v>6440837</v>
+        <v>6440760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4126,42 +4134,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130193547</v>
+        <v>130206059</v>
       </c>
       <c r="B36" t="n">
-        <v>56931</v>
+        <v>79714</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4169,10 +4172,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556301</v>
+        <v>556285</v>
       </c>
       <c r="R36" t="n">
-        <v>6440760</v>
+        <v>6440650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4213,25 +4216,26 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130206059</v>
+        <v>130206077</v>
       </c>
       <c r="B37" t="n">
         <v>79714</v>
@@ -4269,10 +4273,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556285</v>
+        <v>556524</v>
       </c>
       <c r="R37" t="n">
-        <v>6440650</v>
+        <v>6440529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4332,7 +4336,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130206077</v>
+        <v>130193214</v>
       </c>
       <c r="B38" t="n">
         <v>79714</v>
@@ -4361,19 +4365,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556524</v>
+        <v>556550</v>
       </c>
       <c r="R38" t="n">
-        <v>6440529</v>
+        <v>6440532</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,19 +4415,18 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192475</v>
+        <v>130207870</v>
       </c>
       <c r="B2" t="n">
         <v>56931</v>
@@ -703,25 +703,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556371</v>
+        <v>555987</v>
       </c>
       <c r="R2" t="n">
-        <v>6440485</v>
+        <v>6440734</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,19 +772,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130206069</v>
+        <v>130192475</v>
       </c>
       <c r="B3" t="n">
         <v>56931</v>
@@ -823,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556351</v>
+        <v>556371</v>
       </c>
       <c r="R3" t="n">
-        <v>6440550</v>
+        <v>6440485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,49 +877,54 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130205932</v>
+        <v>130206069</v>
       </c>
       <c r="B4" t="n">
-        <v>79714</v>
+        <v>56931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555963</v>
+        <v>556351</v>
       </c>
       <c r="R4" t="n">
-        <v>6440548</v>
+        <v>6440550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -979,14 +987,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130206032</v>
+        <v>130205932</v>
       </c>
       <c r="B5" t="n">
         <v>79714</v>
@@ -1024,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556137</v>
+        <v>555963</v>
       </c>
       <c r="R5" t="n">
-        <v>6440697</v>
+        <v>6440548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,50 +1088,44 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130192966</v>
+        <v>130206032</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1131,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556440</v>
+        <v>556137</v>
       </c>
       <c r="R6" t="n">
-        <v>6440510</v>
+        <v>6440697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,52 +1184,53 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130206062</v>
+        <v>130192966</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1237,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556289</v>
+        <v>556440</v>
       </c>
       <c r="R7" t="n">
-        <v>6440643</v>
+        <v>6440510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,75 +1284,72 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207870</v>
+        <v>130206062</v>
       </c>
       <c r="B8" t="n">
-        <v>56931</v>
+        <v>57738</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555987</v>
+        <v>556289</v>
       </c>
       <c r="R8" t="n">
-        <v>6440734</v>
+        <v>6440643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,12 +1396,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130207870</v>
+        <v>130192475</v>
       </c>
       <c r="B2" t="n">
         <v>56931</v>
@@ -703,29 +703,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555987</v>
+        <v>556371</v>
       </c>
       <c r="R2" t="n">
-        <v>6440734</v>
+        <v>6440485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,22 +768,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192475</v>
+        <v>130192966</v>
       </c>
       <c r="B3" t="n">
-        <v>56931</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,29 +791,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -827,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556371</v>
+        <v>556440</v>
       </c>
       <c r="R3" t="n">
-        <v>6440485</v>
+        <v>6440510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,14 +880,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206069</v>
+        <v>130207870</v>
       </c>
       <c r="B4" t="n">
         <v>56931</v>
@@ -917,25 +915,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556351</v>
+        <v>555987</v>
       </c>
       <c r="R4" t="n">
-        <v>6440550</v>
+        <v>6440734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,49 +984,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130205932</v>
+        <v>130206069</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>56931</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555963</v>
+        <v>556351</v>
       </c>
       <c r="R5" t="n">
-        <v>6440548</v>
+        <v>6440550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1083,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1088,17 +1094,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206032</v>
+        <v>130206062</v>
       </c>
       <c r="B6" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,26 +1112,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1133,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556137</v>
+        <v>556289</v>
       </c>
       <c r="R6" t="n">
-        <v>6440697</v>
+        <v>6440643</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,7 +1188,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,43 +1206,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130192966</v>
+        <v>130205932</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79714</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1240,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556440</v>
+        <v>555963</v>
       </c>
       <c r="R7" t="n">
-        <v>6440510</v>
+        <v>6440548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,22 +1295,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130206062</v>
+        <v>130206032</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,31 +1318,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1346,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556289</v>
+        <v>556137</v>
       </c>
       <c r="R8" t="n">
-        <v>6440643</v>
+        <v>6440697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,6 +1389,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>130205883</v>
       </c>
       <c r="B10" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>130206011</v>
       </c>
       <c r="B11" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130205999</v>
+        <v>130206042</v>
       </c>
       <c r="B14" t="n">
-        <v>91660</v>
+        <v>92915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556087</v>
+        <v>556130</v>
       </c>
       <c r="R14" t="n">
-        <v>6440692</v>
+        <v>6440718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130206042</v>
+        <v>130205999</v>
       </c>
       <c r="B15" t="n">
-        <v>92913</v>
+        <v>91662</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556130</v>
+        <v>556087</v>
       </c>
       <c r="R15" t="n">
-        <v>6440718</v>
+        <v>6440692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2522,7 +2522,7 @@
         <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130191022</v>
+        <v>130181235</v>
       </c>
       <c r="B23" t="n">
-        <v>56931</v>
+        <v>92923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,42 +2821,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556359</v>
+        <v>555982</v>
       </c>
       <c r="R23" t="n">
-        <v>6440535</v>
+        <v>6440530</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2915,10 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130188529</v>
+        <v>130191022</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>56931</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,30 +2918,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2959,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556326</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>6440589</v>
+        <v>6440535</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,7 +2994,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3012,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130181235</v>
+        <v>130188529</v>
       </c>
       <c r="B25" t="n">
-        <v>92921</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,34 +3023,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555982</v>
+        <v>556326</v>
       </c>
       <c r="R25" t="n">
-        <v>6440530</v>
+        <v>6440589</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130206076</v>
+        <v>130184293</v>
       </c>
       <c r="B26" t="n">
-        <v>92921</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,37 +3130,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556535</v>
+        <v>556081</v>
       </c>
       <c r="R26" t="n">
-        <v>6440485</v>
+        <v>6440690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,19 +3198,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3430,10 +3426,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130184293</v>
+        <v>130206076</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>92923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,34 +3437,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556081</v>
+        <v>556535</v>
       </c>
       <c r="R29" t="n">
-        <v>6440690</v>
+        <v>6440485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,67 +3508,64 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130206072</v>
+        <v>130181118</v>
       </c>
       <c r="B30" t="n">
-        <v>96320</v>
+        <v>79714</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556413</v>
+        <v>555982</v>
       </c>
       <c r="R30" t="n">
-        <v>6440503</v>
+        <v>6440530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,64 +3606,67 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130181118</v>
+        <v>130206072</v>
       </c>
       <c r="B31" t="n">
-        <v>79714</v>
+        <v>96322</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555982</v>
+        <v>556413</v>
       </c>
       <c r="R31" t="n">
-        <v>6440530</v>
+        <v>6440503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,63 +3707,72 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130191846</v>
+        <v>130193838</v>
       </c>
       <c r="B32" t="n">
-        <v>78761</v>
+        <v>56931</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556374</v>
+        <v>556003</v>
       </c>
       <c r="R32" t="n">
-        <v>6440510</v>
+        <v>6440837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,53 +3932,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130193838</v>
+        <v>130191846</v>
       </c>
       <c r="B34" t="n">
-        <v>56931</v>
+        <v>78761</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556003</v>
+        <v>556374</v>
       </c>
       <c r="R34" t="n">
-        <v>6440837</v>
+        <v>6440510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130192475</v>
       </c>
       <c r="B2" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,57 +887,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130207870</v>
+        <v>130206062</v>
       </c>
       <c r="B4" t="n">
-        <v>56931</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555987</v>
+        <v>556289</v>
       </c>
       <c r="R4" t="n">
-        <v>6440734</v>
+        <v>6440643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,54 +980,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130206069</v>
+        <v>130205932</v>
       </c>
       <c r="B5" t="n">
-        <v>56931</v>
+        <v>79799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556351</v>
+        <v>555963</v>
       </c>
       <c r="R5" t="n">
-        <v>6440550</v>
+        <v>6440548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1094,17 +1086,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206062</v>
+        <v>130206032</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,31 +1104,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556289</v>
+        <v>556137</v>
       </c>
       <c r="R6" t="n">
-        <v>6440643</v>
+        <v>6440697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,6 +1175,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,37 +1194,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130205932</v>
+        <v>130206069</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>57016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1244,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555963</v>
+        <v>556351</v>
       </c>
       <c r="R7" t="n">
-        <v>6440548</v>
+        <v>6440550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1281,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1300,55 +1292,64 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130206032</v>
+        <v>130207870</v>
       </c>
       <c r="B8" t="n">
-        <v>79714</v>
+        <v>57016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556137</v>
+        <v>555987</v>
       </c>
       <c r="R8" t="n">
-        <v>6440697</v>
+        <v>6440734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,19 +1390,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1411,7 +1411,7 @@
         <v>130188519</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>130205883</v>
       </c>
       <c r="B10" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>130206011</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130184588</v>
       </c>
       <c r="B12" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>130206073</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130206042</v>
+        <v>130205992</v>
       </c>
       <c r="B14" t="n">
-        <v>92915</v>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556130</v>
+        <v>555991</v>
       </c>
       <c r="R14" t="n">
-        <v>6440718</v>
+        <v>6440609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130205999</v>
+        <v>130206042</v>
       </c>
       <c r="B15" t="n">
-        <v>91662</v>
+        <v>93002</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556087</v>
+        <v>556130</v>
       </c>
       <c r="R15" t="n">
-        <v>6440692</v>
+        <v>6440718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130205992</v>
+        <v>130205999</v>
       </c>
       <c r="B16" t="n">
-        <v>79714</v>
+        <v>91749</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,21 +2126,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555991</v>
+        <v>556087</v>
       </c>
       <c r="R16" t="n">
-        <v>6440609</v>
+        <v>6440692</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
         <v>130184338</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>130184193</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>130206066</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>130188670</v>
       </c>
       <c r="B21" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>130186120</v>
       </c>
       <c r="B22" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130181235</v>
+        <v>130191022</v>
       </c>
       <c r="B23" t="n">
-        <v>92923</v>
+        <v>57016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,34 +2821,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555982</v>
+        <v>556359</v>
       </c>
       <c r="R23" t="n">
-        <v>6440530</v>
+        <v>6440535</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2907,10 +2915,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130191022</v>
+        <v>130188529</v>
       </c>
       <c r="B24" t="n">
-        <v>56931</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,29 +2926,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2950,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556359</v>
+        <v>556326</v>
       </c>
       <c r="R24" t="n">
-        <v>6440535</v>
+        <v>6440589</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,6 +3003,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3012,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130188529</v>
+        <v>130181235</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3023,43 +3033,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556326</v>
+        <v>555982</v>
       </c>
       <c r="R25" t="n">
-        <v>6440589</v>
+        <v>6440530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,7 +3101,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>130206002</v>
       </c>
       <c r="B27" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3321,42 +3321,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130205958</v>
+        <v>130206076</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>93010</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556008</v>
+        <v>556535</v>
       </c>
       <c r="R28" t="n">
-        <v>6440596</v>
+        <v>6440485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3408,6 +3403,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3419,44 +3415,49 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130206076</v>
+        <v>130205958</v>
       </c>
       <c r="B29" t="n">
-        <v>92923</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3464,10 +3465,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556535</v>
+        <v>556008</v>
       </c>
       <c r="R29" t="n">
-        <v>6440485</v>
+        <v>6440596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,7 +3509,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
         <v>130181118</v>
       </c>
       <c r="B30" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>130206072</v>
       </c>
       <c r="B31" t="n">
-        <v>96322</v>
+        <v>96409</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3726,53 +3726,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130193838</v>
+        <v>130191846</v>
       </c>
       <c r="B32" t="n">
-        <v>56931</v>
+        <v>78846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556003</v>
+        <v>556374</v>
       </c>
       <c r="R32" t="n">
-        <v>6440837</v>
+        <v>6440510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3831,37 +3823,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130206052</v>
+        <v>130193838</v>
       </c>
       <c r="B33" t="n">
-        <v>79714</v>
+        <v>57016</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3869,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556177</v>
+        <v>556003</v>
       </c>
       <c r="R33" t="n">
-        <v>6440700</v>
+        <v>6440837</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3913,29 +3910,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B34" t="n">
-        <v>78761</v>
+        <v>79799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,34 +3939,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R34" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4011,18 +4010,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
         <v>130193547</v>
       </c>
       <c r="B35" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>130206059</v>
       </c>
       <c r="B36" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>130206077</v>
       </c>
       <c r="B37" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>130193214</v>
       </c>
       <c r="B38" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -3119,45 +3119,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130184293</v>
+        <v>130206002</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556081</v>
+        <v>556108</v>
       </c>
       <c r="R26" t="n">
-        <v>6440690</v>
+        <v>6440698</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,54 +3212,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206002</v>
+        <v>130206076</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>93010</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3259,10 +3262,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556108</v>
+        <v>556535</v>
       </c>
       <c r="R27" t="n">
-        <v>6440698</v>
+        <v>6440485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3303,6 +3306,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3321,37 +3325,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130206076</v>
+        <v>130205958</v>
       </c>
       <c r="B28" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3359,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556535</v>
+        <v>556008</v>
       </c>
       <c r="R28" t="n">
-        <v>6440485</v>
+        <v>6440596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3403,7 +3412,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3415,60 +3423,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130205958</v>
+        <v>130184293</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556008</v>
+        <v>556081</v>
       </c>
       <c r="R29" t="n">
-        <v>6440596</v>
+        <v>6440690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,12 +3515,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192475</v>
+        <v>130206062</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556371</v>
+        <v>556289</v>
       </c>
       <c r="R2" t="n">
-        <v>6440485</v>
+        <v>6440643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,55 +768,49 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192966</v>
+        <v>130205932</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556440</v>
+        <v>555963</v>
       </c>
       <c r="R3" t="n">
-        <v>6440510</v>
+        <v>6440548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +869,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206062</v>
+        <v>130206032</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +892,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556289</v>
+        <v>556137</v>
       </c>
       <c r="R4" t="n">
-        <v>6440643</v>
+        <v>6440697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,48 +982,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130205932</v>
+        <v>130207870</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555963</v>
+        <v>555987</v>
       </c>
       <c r="R5" t="n">
-        <v>6440548</v>
+        <v>6440734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,56 +1073,60 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206032</v>
+        <v>130206069</v>
       </c>
       <c r="B6" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1131,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556137</v>
+        <v>556351</v>
       </c>
       <c r="R6" t="n">
-        <v>6440697</v>
+        <v>6440550</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1178,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1194,7 +1196,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130206069</v>
+        <v>130192475</v>
       </c>
       <c r="B7" t="n">
         <v>57016</v>
@@ -1237,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556351</v>
+        <v>556371</v>
       </c>
       <c r="R7" t="n">
-        <v>6440550</v>
+        <v>6440485</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,22 +1289,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130207870</v>
+        <v>130192966</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1310,46 +1312,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555987</v>
+        <v>556440</v>
       </c>
       <c r="R8" t="n">
-        <v>6440734</v>
+        <v>6440510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,18 +1389,19 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130205992</v>
+        <v>130206042</v>
       </c>
       <c r="B14" t="n">
-        <v>79799</v>
+        <v>93002</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555991</v>
+        <v>556130</v>
       </c>
       <c r="R14" t="n">
-        <v>6440609</v>
+        <v>6440718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130206042</v>
+        <v>130205992</v>
       </c>
       <c r="B15" t="n">
-        <v>93002</v>
+        <v>79799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556130</v>
+        <v>555991</v>
       </c>
       <c r="R15" t="n">
-        <v>6440718</v>
+        <v>6440609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130191022</v>
+        <v>130181235</v>
       </c>
       <c r="B23" t="n">
-        <v>57016</v>
+        <v>93010</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,42 +2821,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556359</v>
+        <v>555982</v>
       </c>
       <c r="R23" t="n">
-        <v>6440535</v>
+        <v>6440530</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2915,10 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130188529</v>
+        <v>130191022</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>57016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,30 +2918,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2959,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556326</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>6440589</v>
+        <v>6440535</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,7 +2994,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3012,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130181235</v>
+        <v>130188529</v>
       </c>
       <c r="B25" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,34 +3023,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555982</v>
+        <v>556326</v>
       </c>
       <c r="R25" t="n">
-        <v>6440530</v>
+        <v>6440589</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3119,53 +3119,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130206002</v>
+        <v>130184293</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556108</v>
+        <v>556081</v>
       </c>
       <c r="R26" t="n">
-        <v>6440698</v>
+        <v>6440690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,12 +3204,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3325,7 +3317,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130205958</v>
+        <v>130206002</v>
       </c>
       <c r="B28" t="n">
         <v>57823</v>
@@ -3368,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556008</v>
+        <v>556108</v>
       </c>
       <c r="R28" t="n">
-        <v>6440596</v>
+        <v>6440698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,52 +3415,60 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130184293</v>
+        <v>130205958</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556081</v>
+        <v>556008</v>
       </c>
       <c r="R29" t="n">
-        <v>6440690</v>
+        <v>6440596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,12 +3515,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B32" t="n">
-        <v>78846</v>
+        <v>79799</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,34 +3737,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R32" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,71 +3808,64 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130193838</v>
+        <v>130191846</v>
       </c>
       <c r="B33" t="n">
-        <v>57016</v>
+        <v>78846</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556003</v>
+        <v>556374</v>
       </c>
       <c r="R33" t="n">
-        <v>6440837</v>
+        <v>6440510</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,37 +3924,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130206052</v>
+        <v>130193838</v>
       </c>
       <c r="B34" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3966,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556177</v>
+        <v>556003</v>
       </c>
       <c r="R34" t="n">
-        <v>6440700</v>
+        <v>6440837</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4010,19 +4011,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -780,48 +780,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130205932</v>
+        <v>130207870</v>
       </c>
       <c r="B3" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555963</v>
+        <v>555987</v>
       </c>
       <c r="R3" t="n">
-        <v>6440548</v>
+        <v>6440734</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,56 +871,60 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206032</v>
+        <v>130206069</v>
       </c>
       <c r="B4" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -919,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556137</v>
+        <v>556351</v>
       </c>
       <c r="R4" t="n">
-        <v>6440697</v>
+        <v>6440550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +976,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,57 +994,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130207870</v>
+        <v>130205932</v>
       </c>
       <c r="B5" t="n">
-        <v>57016</v>
+        <v>79799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555987</v>
+        <v>555963</v>
       </c>
       <c r="R5" t="n">
-        <v>6440734</v>
+        <v>6440548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,60 +1076,56 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206069</v>
+        <v>130206032</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>79799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556351</v>
+        <v>556137</v>
       </c>
       <c r="R6" t="n">
-        <v>6440550</v>
+        <v>6440697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,6 +1177,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130192475</v>
+        <v>130192966</v>
       </c>
       <c r="B7" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,29 +1207,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1239,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556371</v>
+        <v>556440</v>
       </c>
       <c r="R7" t="n">
-        <v>6440485</v>
+        <v>6440510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,6 +1284,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1294,17 +1296,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192966</v>
+        <v>130192475</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>57016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,30 +1314,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1345,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556440</v>
+        <v>556371</v>
       </c>
       <c r="R8" t="n">
-        <v>6440510</v>
+        <v>6440485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1390,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130205992</v>
+        <v>130205999</v>
       </c>
       <c r="B15" t="n">
-        <v>79799</v>
+        <v>91749</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555991</v>
+        <v>556087</v>
       </c>
       <c r="R15" t="n">
-        <v>6440609</v>
+        <v>6440692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130205999</v>
+        <v>130205992</v>
       </c>
       <c r="B16" t="n">
-        <v>91749</v>
+        <v>79799</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,21 +2126,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556087</v>
+        <v>555991</v>
       </c>
       <c r="R16" t="n">
-        <v>6440692</v>
+        <v>6440609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130191022</v>
+        <v>130188529</v>
       </c>
       <c r="B24" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,29 +2918,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2950,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556359</v>
+        <v>556326</v>
       </c>
       <c r="R24" t="n">
-        <v>6440535</v>
+        <v>6440589</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,6 +2995,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3012,10 +3014,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130188529</v>
+        <v>130191022</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>57016</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3023,30 +3025,29 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3056,10 +3057,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556326</v>
+        <v>556359</v>
       </c>
       <c r="R25" t="n">
-        <v>6440589</v>
+        <v>6440535</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,7 +3101,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130184293</v>
+        <v>130206076</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,34 +3130,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556081</v>
+        <v>556535</v>
       </c>
       <c r="R26" t="n">
-        <v>6440690</v>
+        <v>6440485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3198,28 +3201,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206076</v>
+        <v>130184293</v>
       </c>
       <c r="B27" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,37 +3231,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556535</v>
+        <v>556081</v>
       </c>
       <c r="R27" t="n">
-        <v>6440485</v>
+        <v>6440690</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,19 +3299,18 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130206052</v>
+        <v>130191846</v>
       </c>
       <c r="B32" t="n">
-        <v>79799</v>
+        <v>78846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,37 +3737,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556177</v>
+        <v>556374</v>
       </c>
       <c r="R32" t="n">
-        <v>6440700</v>
+        <v>6440510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3808,29 +3805,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B33" t="n">
-        <v>78846</v>
+        <v>79799</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3838,34 +3834,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R33" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,18 +3905,19 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130206062</v>
+        <v>130192475</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556289</v>
+        <v>556371</v>
       </c>
       <c r="R2" t="n">
-        <v>6440643</v>
+        <v>6440485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,22 +768,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130207870</v>
+        <v>130192966</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,46 +791,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555987</v>
+        <v>556440</v>
       </c>
       <c r="R3" t="n">
-        <v>6440734</v>
+        <v>6440510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,25 +868,26 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206069</v>
+        <v>130207870</v>
       </c>
       <c r="B4" t="n">
         <v>57016</v>
@@ -917,25 +915,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556351</v>
+        <v>555987</v>
       </c>
       <c r="R4" t="n">
-        <v>6440550</v>
+        <v>6440734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,49 +984,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130205932</v>
+        <v>130206069</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555963</v>
+        <v>556351</v>
       </c>
       <c r="R5" t="n">
-        <v>6440548</v>
+        <v>6440550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1083,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1088,14 +1094,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206032</v>
+        <v>130205932</v>
       </c>
       <c r="B6" t="n">
         <v>79799</v>
@@ -1133,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556137</v>
+        <v>555963</v>
       </c>
       <c r="R6" t="n">
-        <v>6440697</v>
+        <v>6440548</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,50 +1195,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130192966</v>
+        <v>130206032</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556440</v>
+        <v>556137</v>
       </c>
       <c r="R7" t="n">
-        <v>6440510</v>
+        <v>6440697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,44 +1291,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192475</v>
+        <v>130206062</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,7 +1336,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556371</v>
+        <v>556289</v>
       </c>
       <c r="R8" t="n">
-        <v>6440485</v>
+        <v>6440643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,12 +1396,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130206042</v>
+        <v>130205992</v>
       </c>
       <c r="B14" t="n">
-        <v>93002</v>
+        <v>79799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556130</v>
+        <v>555991</v>
       </c>
       <c r="R14" t="n">
-        <v>6440718</v>
+        <v>6440609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130205999</v>
+        <v>130206042</v>
       </c>
       <c r="B15" t="n">
-        <v>91749</v>
+        <v>93002</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556087</v>
+        <v>556130</v>
       </c>
       <c r="R15" t="n">
-        <v>6440692</v>
+        <v>6440718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130205992</v>
+        <v>130205999</v>
       </c>
       <c r="B16" t="n">
-        <v>79799</v>
+        <v>91749</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,21 +2126,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555991</v>
+        <v>556087</v>
       </c>
       <c r="R16" t="n">
-        <v>6440609</v>
+        <v>6440692</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130188529</v>
+        <v>130191022</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>57016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,30 +2918,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2951,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556326</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>6440589</v>
+        <v>6440535</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2995,7 +2994,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3014,10 +3012,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130191022</v>
+        <v>130188529</v>
       </c>
       <c r="B25" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3025,29 +3023,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3057,10 +3056,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556359</v>
+        <v>556326</v>
       </c>
       <c r="R25" t="n">
-        <v>6440535</v>
+        <v>6440589</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130206076</v>
+        <v>130184293</v>
       </c>
       <c r="B26" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,37 +3130,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556535</v>
+        <v>556081</v>
       </c>
       <c r="R26" t="n">
-        <v>6440485</v>
+        <v>6440690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,64 +3198,71 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130184293</v>
+        <v>130206002</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556081</v>
+        <v>556108</v>
       </c>
       <c r="R27" t="n">
-        <v>6440690</v>
+        <v>6440698</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3305,19 +3309,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130206002</v>
+        <v>130205958</v>
       </c>
       <c r="B28" t="n">
         <v>57823</v>
@@ -3360,10 +3364,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556108</v>
+        <v>556008</v>
       </c>
       <c r="R28" t="n">
-        <v>6440698</v>
+        <v>6440596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3415,49 +3419,44 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130205958</v>
+        <v>130206076</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>93010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3465,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556008</v>
+        <v>556535</v>
       </c>
       <c r="R29" t="n">
-        <v>6440596</v>
+        <v>6440485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,6 +3508,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3726,45 +3726,53 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130191846</v>
+        <v>130193838</v>
       </c>
       <c r="B32" t="n">
-        <v>78846</v>
+        <v>57016</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556374</v>
+        <v>556003</v>
       </c>
       <c r="R32" t="n">
-        <v>6440510</v>
+        <v>6440837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,53 +3932,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130193838</v>
+        <v>130191846</v>
       </c>
       <c r="B34" t="n">
-        <v>57016</v>
+        <v>78846</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556003</v>
+        <v>556374</v>
       </c>
       <c r="R34" t="n">
-        <v>6440837</v>
+        <v>6440510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192475</v>
+        <v>130192966</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556371</v>
+        <v>556440</v>
       </c>
       <c r="R2" t="n">
-        <v>6440485</v>
+        <v>6440510</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -773,17 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192966</v>
+        <v>130192475</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,30 +793,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -824,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556440</v>
+        <v>556371</v>
       </c>
       <c r="R3" t="n">
-        <v>6440510</v>
+        <v>6440485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,7 +869,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,60 +880,64 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206062</v>
+        <v>130207870</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556289</v>
+        <v>555987</v>
       </c>
       <c r="R4" t="n">
-        <v>6440643</v>
+        <v>6440734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,49 +984,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130205932</v>
+        <v>130206069</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1030,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555963</v>
+        <v>556351</v>
       </c>
       <c r="R5" t="n">
-        <v>6440548</v>
+        <v>6440550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1083,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1086,17 +1094,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206032</v>
+        <v>130206062</v>
       </c>
       <c r="B6" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,26 +1112,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1131,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556137</v>
+        <v>556289</v>
       </c>
       <c r="R6" t="n">
-        <v>6440697</v>
+        <v>6440643</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1188,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1194,57 +1206,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130207870</v>
+        <v>130205932</v>
       </c>
       <c r="B7" t="n">
-        <v>57016</v>
+        <v>79799</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555987</v>
+        <v>555963</v>
       </c>
       <c r="R7" t="n">
-        <v>6440734</v>
+        <v>6440548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,60 +1288,56 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130206069</v>
+        <v>130206032</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>79799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1346,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556351</v>
+        <v>556137</v>
       </c>
       <c r="R8" t="n">
-        <v>6440550</v>
+        <v>6440697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,6 +1389,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -3119,45 +3119,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130184293</v>
+        <v>130206002</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556081</v>
+        <v>556108</v>
       </c>
       <c r="R26" t="n">
-        <v>6440690</v>
+        <v>6440698</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,49 +3212,54 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206076</v>
+        <v>130205958</v>
       </c>
       <c r="B27" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3254,10 +3267,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556535</v>
+        <v>556008</v>
       </c>
       <c r="R27" t="n">
-        <v>6440485</v>
+        <v>6440596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,7 +3311,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3310,60 +3322,52 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130206002</v>
+        <v>130184293</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556108</v>
+        <v>556081</v>
       </c>
       <c r="R28" t="n">
-        <v>6440698</v>
+        <v>6440690</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3410,54 +3414,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130205958</v>
+        <v>130206076</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>93010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3465,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556008</v>
+        <v>556535</v>
       </c>
       <c r="R29" t="n">
-        <v>6440596</v>
+        <v>6440485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,6 +3508,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -2519,10 +2519,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130188670</v>
+        <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>79799</v>
+        <v>91749</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,21 +2530,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556335</v>
+        <v>556081</v>
       </c>
       <c r="R20" t="n">
-        <v>6440570</v>
+        <v>6440690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130184275</v>
+        <v>130188670</v>
       </c>
       <c r="B21" t="n">
-        <v>91749</v>
+        <v>79799</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556081</v>
+        <v>556335</v>
       </c>
       <c r="R21" t="n">
-        <v>6440690</v>
+        <v>6440570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3119,53 +3119,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130206002</v>
+        <v>130184293</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556108</v>
+        <v>556081</v>
       </c>
       <c r="R26" t="n">
-        <v>6440698</v>
+        <v>6440690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,54 +3204,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130205958</v>
+        <v>130206076</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>93010</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3267,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556008</v>
+        <v>556535</v>
       </c>
       <c r="R27" t="n">
-        <v>6440596</v>
+        <v>6440485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,6 +3298,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3322,52 +3310,60 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130184293</v>
+        <v>130206002</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556081</v>
+        <v>556108</v>
       </c>
       <c r="R28" t="n">
-        <v>6440690</v>
+        <v>6440698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3414,49 +3410,54 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130206076</v>
+        <v>130205958</v>
       </c>
       <c r="B29" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3464,10 +3465,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556535</v>
+        <v>556008</v>
       </c>
       <c r="R29" t="n">
-        <v>6440485</v>
+        <v>6440596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,7 +3509,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192966</v>
+        <v>130192475</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556440</v>
+        <v>556371</v>
       </c>
       <c r="R2" t="n">
-        <v>6440510</v>
+        <v>6440485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,17 +773,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192475</v>
+        <v>130192966</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,29 +791,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -825,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556371</v>
+        <v>556440</v>
       </c>
       <c r="R3" t="n">
-        <v>6440485</v>
+        <v>6440510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -880,64 +880,60 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130207870</v>
+        <v>130206062</v>
       </c>
       <c r="B4" t="n">
-        <v>57016</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555987</v>
+        <v>556289</v>
       </c>
       <c r="R4" t="n">
-        <v>6440734</v>
+        <v>6440643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,54 +980,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130206069</v>
+        <v>130205932</v>
       </c>
       <c r="B5" t="n">
-        <v>57016</v>
+        <v>79799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556351</v>
+        <v>555963</v>
       </c>
       <c r="R5" t="n">
-        <v>6440550</v>
+        <v>6440548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,6 +1074,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1094,17 +1086,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206062</v>
+        <v>130206032</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>79799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,31 +1104,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556289</v>
+        <v>556137</v>
       </c>
       <c r="R6" t="n">
-        <v>6440643</v>
+        <v>6440697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,6 +1175,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1206,48 +1194,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130205932</v>
+        <v>130207870</v>
       </c>
       <c r="B7" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555963</v>
+        <v>555987</v>
       </c>
       <c r="R7" t="n">
-        <v>6440548</v>
+        <v>6440734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,56 +1285,60 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130206032</v>
+        <v>130206069</v>
       </c>
       <c r="B8" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1345,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556137</v>
+        <v>556351</v>
       </c>
       <c r="R8" t="n">
-        <v>6440697</v>
+        <v>6440550</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1390,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130188529</v>
+        <v>130191022</v>
       </c>
       <c r="B23" t="n">
-        <v>8451</v>
+        <v>57016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,30 +2821,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -2854,10 +2853,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556326</v>
+        <v>556359</v>
       </c>
       <c r="R23" t="n">
-        <v>6440589</v>
+        <v>6440535</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2898,7 +2897,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2917,10 +2915,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130181235</v>
+        <v>130188529</v>
       </c>
       <c r="B24" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2928,34 +2926,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555982</v>
+        <v>556326</v>
       </c>
       <c r="R24" t="n">
-        <v>6440530</v>
+        <v>6440589</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2996,6 +3003,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3014,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130191022</v>
+        <v>130181235</v>
       </c>
       <c r="B25" t="n">
-        <v>57016</v>
+        <v>93010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3025,42 +3033,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556359</v>
+        <v>555982</v>
       </c>
       <c r="R25" t="n">
-        <v>6440535</v>
+        <v>6440530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3119,45 +3119,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130184293</v>
+        <v>130206002</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556081</v>
+        <v>556108</v>
       </c>
       <c r="R26" t="n">
-        <v>6440690</v>
+        <v>6440698</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3204,49 +3212,54 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206076</v>
+        <v>130205958</v>
       </c>
       <c r="B27" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3254,10 +3267,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556535</v>
+        <v>556008</v>
       </c>
       <c r="R27" t="n">
-        <v>6440485</v>
+        <v>6440596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,7 +3311,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3310,60 +3322,52 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130206002</v>
+        <v>130184293</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556108</v>
+        <v>556081</v>
       </c>
       <c r="R28" t="n">
-        <v>6440698</v>
+        <v>6440690</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3410,54 +3414,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130205958</v>
+        <v>130206076</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>93010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3465,10 +3464,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556008</v>
+        <v>556535</v>
       </c>
       <c r="R29" t="n">
-        <v>6440596</v>
+        <v>6440485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,6 +3508,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192475</v>
+        <v>130192966</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556371</v>
+        <v>556440</v>
       </c>
       <c r="R2" t="n">
-        <v>6440485</v>
+        <v>6440510</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -773,50 +775,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192966</v>
+        <v>130205932</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79802</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556440</v>
+        <v>555963</v>
       </c>
       <c r="R3" t="n">
-        <v>6440510</v>
+        <v>6440548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +871,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206062</v>
+        <v>130206032</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>79802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,31 +894,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556289</v>
+        <v>556137</v>
       </c>
       <c r="R4" t="n">
-        <v>6440643</v>
+        <v>6440697</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,6 +965,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,10 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130205932</v>
+        <v>130206062</v>
       </c>
       <c r="B5" t="n">
-        <v>79799</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,26 +995,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1030,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555963</v>
+        <v>556289</v>
       </c>
       <c r="R5" t="n">
-        <v>6440548</v>
+        <v>6440643</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1071,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1086,44 +1082,49 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206032</v>
+        <v>130192475</v>
       </c>
       <c r="B6" t="n">
-        <v>79799</v>
+        <v>57016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1131,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556137</v>
+        <v>556371</v>
       </c>
       <c r="R6" t="n">
-        <v>6440697</v>
+        <v>6440485</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,19 +1176,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1516,7 +1516,7 @@
         <v>130205883</v>
       </c>
       <c r="B10" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>130206011</v>
       </c>
       <c r="B11" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130184588</v>
       </c>
       <c r="B12" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1815,7 +1815,7 @@
         <v>130206073</v>
       </c>
       <c r="B13" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130206042</v>
+        <v>130205992</v>
       </c>
       <c r="B14" t="n">
-        <v>93002</v>
+        <v>79802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556130</v>
+        <v>555991</v>
       </c>
       <c r="R14" t="n">
-        <v>6440718</v>
+        <v>6440609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130205999</v>
+        <v>130206042</v>
       </c>
       <c r="B15" t="n">
-        <v>91749</v>
+        <v>93005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556087</v>
+        <v>556130</v>
       </c>
       <c r="R15" t="n">
-        <v>6440692</v>
+        <v>6440718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130205992</v>
+        <v>130205999</v>
       </c>
       <c r="B16" t="n">
-        <v>79799</v>
+        <v>91752</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,21 +2126,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555991</v>
+        <v>556087</v>
       </c>
       <c r="R16" t="n">
-        <v>6440609</v>
+        <v>6440692</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2324,7 +2324,7 @@
         <v>130184193</v>
       </c>
       <c r="B18" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2421,7 +2421,7 @@
         <v>130206066</v>
       </c>
       <c r="B19" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
         <v>130188670</v>
       </c>
       <c r="B21" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
         <v>130186120</v>
       </c>
       <c r="B22" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
         <v>130181235</v>
       </c>
       <c r="B25" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3112,60 +3112,52 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130206002</v>
+        <v>130184293</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556108</v>
+        <v>556081</v>
       </c>
       <c r="R26" t="n">
-        <v>6440698</v>
+        <v>6440690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,54 +3204,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130205958</v>
+        <v>130206076</v>
       </c>
       <c r="B27" t="n">
-        <v>57823</v>
+        <v>93013</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3267,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556008</v>
+        <v>556535</v>
       </c>
       <c r="R27" t="n">
-        <v>6440596</v>
+        <v>6440485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,6 +3298,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3322,52 +3310,60 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130184293</v>
+        <v>130206002</v>
       </c>
       <c r="B28" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556081</v>
+        <v>556108</v>
       </c>
       <c r="R28" t="n">
-        <v>6440690</v>
+        <v>6440698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3414,49 +3410,54 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130206076</v>
+        <v>130205958</v>
       </c>
       <c r="B29" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3464,10 +3465,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556535</v>
+        <v>556008</v>
       </c>
       <c r="R29" t="n">
-        <v>6440485</v>
+        <v>6440596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3508,7 +3509,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3520,52 +3520,56 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130181118</v>
+        <v>130206072</v>
       </c>
       <c r="B30" t="n">
-        <v>79799</v>
+        <v>96412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555982</v>
+        <v>556413</v>
       </c>
       <c r="R30" t="n">
-        <v>6440530</v>
+        <v>6440503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,67 +3610,64 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130206072</v>
+        <v>130181118</v>
       </c>
       <c r="B31" t="n">
-        <v>96409</v>
+        <v>79802</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556413</v>
+        <v>555982</v>
       </c>
       <c r="R31" t="n">
-        <v>6440503</v>
+        <v>6440530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,29 +3708,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130206052</v>
+        <v>130191846</v>
       </c>
       <c r="B32" t="n">
-        <v>79799</v>
+        <v>78849</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,37 +3737,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556177</v>
+        <v>556374</v>
       </c>
       <c r="R32" t="n">
-        <v>6440700</v>
+        <v>6440510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3808,19 +3805,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3925,17 +3921,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B34" t="n">
-        <v>78846</v>
+        <v>79802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,34 +3939,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R34" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4011,18 +4010,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4137,7 +4137,7 @@
         <v>130206059</v>
       </c>
       <c r="B36" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>130206077</v>
       </c>
       <c r="B37" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>130193214</v>
       </c>
       <c r="B38" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,41 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192966</v>
+        <v>130206062</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556440</v>
+        <v>556289</v>
       </c>
       <c r="R2" t="n">
-        <v>6440510</v>
+        <v>6440643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,56 +762,61 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130205932</v>
+        <v>130192966</v>
       </c>
       <c r="B3" t="n">
-        <v>79802</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555963</v>
+        <v>556440</v>
       </c>
       <c r="R3" t="n">
-        <v>6440548</v>
+        <v>6440510</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206032</v>
+        <v>130205932</v>
       </c>
       <c r="B4" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556137</v>
+        <v>555963</v>
       </c>
       <c r="R4" t="n">
-        <v>6440697</v>
+        <v>6440548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,17 +981,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130206062</v>
+        <v>130206032</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>79828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -995,31 +999,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1027,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556289</v>
+        <v>556137</v>
       </c>
       <c r="R5" t="n">
-        <v>6440643</v>
+        <v>6440697</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,6 +1070,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130192475</v>
+        <v>130207870</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,25 +1117,29 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556371</v>
+        <v>555987</v>
       </c>
       <c r="R6" t="n">
-        <v>6440485</v>
+        <v>6440734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,22 +1186,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130207870</v>
+        <v>130206069</v>
       </c>
       <c r="B7" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,29 +1226,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555987</v>
+        <v>556351</v>
       </c>
       <c r="R7" t="n">
-        <v>6440734</v>
+        <v>6440550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,22 +1291,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130206069</v>
+        <v>130192475</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556351</v>
+        <v>556371</v>
       </c>
       <c r="R8" t="n">
-        <v>6440550</v>
+        <v>6440485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,12 +1396,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1411,7 +1411,7 @@
         <v>130188519</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>130205883</v>
       </c>
       <c r="B10" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>130206011</v>
       </c>
       <c r="B11" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         <v>130184588</v>
       </c>
       <c r="B12" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>130206073</v>
       </c>
       <c r="B13" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130205992</v>
+        <v>130206042</v>
       </c>
       <c r="B14" t="n">
-        <v>79802</v>
+        <v>93031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555991</v>
+        <v>556130</v>
       </c>
       <c r="R14" t="n">
-        <v>6440609</v>
+        <v>6440718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130206042</v>
+        <v>130205999</v>
       </c>
       <c r="B15" t="n">
-        <v>93005</v>
+        <v>91778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556130</v>
+        <v>556087</v>
       </c>
       <c r="R15" t="n">
-        <v>6440718</v>
+        <v>6440692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,10 +2115,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130205999</v>
+        <v>130205992</v>
       </c>
       <c r="B16" t="n">
-        <v>91752</v>
+        <v>79828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2126,21 +2126,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>556087</v>
+        <v>555991</v>
       </c>
       <c r="R16" t="n">
-        <v>6440692</v>
+        <v>6440609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
         <v>130184338</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>130184193</v>
       </c>
       <c r="B18" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>130206066</v>
       </c>
       <c r="B19" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130184275</v>
+        <v>130188670</v>
       </c>
       <c r="B20" t="n">
-        <v>91752</v>
+        <v>79828</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,21 +2530,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556081</v>
+        <v>556335</v>
       </c>
       <c r="R20" t="n">
-        <v>6440690</v>
+        <v>6440570</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130188670</v>
+        <v>130184275</v>
       </c>
       <c r="B21" t="n">
-        <v>79802</v>
+        <v>91778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556335</v>
+        <v>556081</v>
       </c>
       <c r="R21" t="n">
-        <v>6440570</v>
+        <v>6440690</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,7 +2716,7 @@
         <v>130186120</v>
       </c>
       <c r="B22" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
         <v>130191022</v>
       </c>
       <c r="B23" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130188529</v>
+        <v>130181235</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>93039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,43 +2926,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556326</v>
+        <v>555982</v>
       </c>
       <c r="R24" t="n">
-        <v>6440589</v>
+        <v>6440530</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,7 +2994,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3012,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130181235</v>
+        <v>130188529</v>
       </c>
       <c r="B25" t="n">
-        <v>93013</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,34 +3023,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555982</v>
+        <v>556326</v>
       </c>
       <c r="R25" t="n">
-        <v>6440530</v>
+        <v>6440589</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130184293</v>
+        <v>130206076</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>93039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,34 +3130,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556081</v>
+        <v>556535</v>
       </c>
       <c r="R26" t="n">
-        <v>6440690</v>
+        <v>6440485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3198,55 +3201,61 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206076</v>
+        <v>130206002</v>
       </c>
       <c r="B27" t="n">
-        <v>93013</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3254,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556535</v>
+        <v>556108</v>
       </c>
       <c r="R27" t="n">
-        <v>6440485</v>
+        <v>6440698</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,7 +3307,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3317,10 +3325,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130206002</v>
+        <v>130205958</v>
       </c>
       <c r="B28" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3360,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556108</v>
+        <v>556008</v>
       </c>
       <c r="R28" t="n">
-        <v>6440698</v>
+        <v>6440596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3415,60 +3423,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130205958</v>
+        <v>130184293</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556008</v>
+        <v>556081</v>
       </c>
       <c r="R29" t="n">
-        <v>6440596</v>
+        <v>6440690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,12 +3515,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
         <v>130206072</v>
       </c>
       <c r="B30" t="n">
-        <v>96412</v>
+        <v>96438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>130181118</v>
       </c>
       <c r="B31" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B32" t="n">
-        <v>78849</v>
+        <v>79828</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,34 +3737,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R32" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,71 +3808,64 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130193838</v>
+        <v>130191846</v>
       </c>
       <c r="B33" t="n">
-        <v>57016</v>
+        <v>78875</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556003</v>
+        <v>556374</v>
       </c>
       <c r="R33" t="n">
-        <v>6440837</v>
+        <v>6440510</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,37 +3924,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130206052</v>
+        <v>130193838</v>
       </c>
       <c r="B34" t="n">
-        <v>79802</v>
+        <v>57042</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3966,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556177</v>
+        <v>556003</v>
       </c>
       <c r="R34" t="n">
-        <v>6440700</v>
+        <v>6440837</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4010,19 +4011,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4032,7 +4032,7 @@
         <v>130193547</v>
       </c>
       <c r="B35" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>130206059</v>
       </c>
       <c r="B36" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>130206077</v>
       </c>
       <c r="B37" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>130193214</v>
       </c>
       <c r="B38" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130206062</v>
+        <v>130205932</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>79828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556289</v>
+        <v>555963</v>
       </c>
       <c r="R2" t="n">
-        <v>6440643</v>
+        <v>6440548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -773,50 +769,44 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192966</v>
+        <v>130206032</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>79828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556440</v>
+        <v>556137</v>
       </c>
       <c r="R3" t="n">
-        <v>6440510</v>
+        <v>6440697</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +865,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130205932</v>
+        <v>130206062</v>
       </c>
       <c r="B4" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,26 +888,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -925,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555963</v>
+        <v>556289</v>
       </c>
       <c r="R4" t="n">
-        <v>6440548</v>
+        <v>6440643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,44 +975,49 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130206032</v>
+        <v>130192475</v>
       </c>
       <c r="B5" t="n">
-        <v>79828</v>
+        <v>57042</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1026,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556137</v>
+        <v>556371</v>
       </c>
       <c r="R5" t="n">
-        <v>6440697</v>
+        <v>6440485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,19 +1069,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1303,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192475</v>
+        <v>130192966</v>
       </c>
       <c r="B8" t="n">
-        <v>57042</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,29 +1312,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1346,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556371</v>
+        <v>556440</v>
       </c>
       <c r="R8" t="n">
-        <v>6440485</v>
+        <v>6440510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,6 +1389,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130188670</v>
+        <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>79828</v>
+        <v>91778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,21 +2530,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556335</v>
+        <v>556081</v>
       </c>
       <c r="R20" t="n">
-        <v>6440570</v>
+        <v>6440690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130184275</v>
+        <v>130188670</v>
       </c>
       <c r="B21" t="n">
-        <v>91778</v>
+        <v>79828</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556081</v>
+        <v>556335</v>
       </c>
       <c r="R21" t="n">
-        <v>6440690</v>
+        <v>6440570</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -877,53 +877,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206062</v>
+        <v>130207870</v>
       </c>
       <c r="B4" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556289</v>
+        <v>555987</v>
       </c>
       <c r="R4" t="n">
-        <v>6440643</v>
+        <v>6440734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130192475</v>
+        <v>130206069</v>
       </c>
       <c r="B5" t="n">
         <v>57042</v>
@@ -1025,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556371</v>
+        <v>556351</v>
       </c>
       <c r="R5" t="n">
-        <v>6440485</v>
+        <v>6440550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,69 +1079,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130207870</v>
+        <v>130206062</v>
       </c>
       <c r="B6" t="n">
-        <v>57042</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555987</v>
+        <v>556289</v>
       </c>
       <c r="R6" t="n">
-        <v>6440734</v>
+        <v>6440643</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,22 +1184,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130206069</v>
+        <v>130192966</v>
       </c>
       <c r="B7" t="n">
-        <v>57042</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,29 +1207,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1239,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556351</v>
+        <v>556440</v>
       </c>
       <c r="R7" t="n">
-        <v>6440550</v>
+        <v>6440510</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,28 +1284,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192966</v>
+        <v>130192475</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>57042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,30 +1314,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1345,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556440</v>
+        <v>556371</v>
       </c>
       <c r="R8" t="n">
-        <v>6440510</v>
+        <v>6440485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1390,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1516,7 +1516,7 @@
         <v>130205883</v>
       </c>
       <c r="B10" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>130206011</v>
       </c>
       <c r="B11" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>130206042</v>
       </c>
       <c r="B14" t="n">
-        <v>93031</v>
+        <v>93032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>130205999</v>
       </c>
       <c r="B15" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130191022</v>
+        <v>130181235</v>
       </c>
       <c r="B23" t="n">
-        <v>57042</v>
+        <v>93040</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,42 +2821,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556359</v>
+        <v>555982</v>
       </c>
       <c r="R23" t="n">
-        <v>6440535</v>
+        <v>6440530</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2915,10 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130181235</v>
+        <v>130191022</v>
       </c>
       <c r="B24" t="n">
-        <v>93039</v>
+        <v>57042</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,34 +2918,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>555982</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>6440530</v>
+        <v>6440535</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130206076</v>
+        <v>130184293</v>
       </c>
       <c r="B26" t="n">
-        <v>93039</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,37 +3130,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556535</v>
+        <v>556081</v>
       </c>
       <c r="R26" t="n">
-        <v>6440485</v>
+        <v>6440690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,61 +3198,55 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206002</v>
+        <v>130206076</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>93040</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3263,10 +3254,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556108</v>
+        <v>556535</v>
       </c>
       <c r="R27" t="n">
-        <v>6440698</v>
+        <v>6440485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3307,6 +3298,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3325,7 +3317,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130205958</v>
+        <v>130206002</v>
       </c>
       <c r="B28" t="n">
         <v>57849</v>
@@ -3368,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556008</v>
+        <v>556108</v>
       </c>
       <c r="R28" t="n">
-        <v>6440596</v>
+        <v>6440698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,52 +3415,60 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130184293</v>
+        <v>130205958</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57849</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556081</v>
+        <v>556008</v>
       </c>
       <c r="R29" t="n">
-        <v>6440690</v>
+        <v>6440596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,12 +3515,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3530,7 +3530,7 @@
         <v>130206072</v>
       </c>
       <c r="B30" t="n">
-        <v>96438</v>
+        <v>96439</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3726,37 +3726,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130206052</v>
+        <v>130193838</v>
       </c>
       <c r="B32" t="n">
-        <v>79828</v>
+        <v>57042</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3764,10 +3769,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556177</v>
+        <v>556003</v>
       </c>
       <c r="R32" t="n">
-        <v>6440700</v>
+        <v>6440837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3808,19 +3813,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3924,42 +3928,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130193838</v>
+        <v>130206052</v>
       </c>
       <c r="B34" t="n">
-        <v>57042</v>
+        <v>79828</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3967,10 +3966,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556003</v>
+        <v>556177</v>
       </c>
       <c r="R34" t="n">
-        <v>6440837</v>
+        <v>6440700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4011,18 +4010,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,37 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130205932</v>
+        <v>130206069</v>
       </c>
       <c r="B2" t="n">
-        <v>79828</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555963</v>
+        <v>556351</v>
       </c>
       <c r="R2" t="n">
-        <v>6440548</v>
+        <v>6440550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -769,17 +773,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130206032</v>
+        <v>130206062</v>
       </c>
       <c r="B3" t="n">
-        <v>79828</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,26 +791,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -814,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556137</v>
+        <v>556289</v>
       </c>
       <c r="R3" t="n">
-        <v>6440697</v>
+        <v>6440643</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,7 +867,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,64 +878,55 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130207870</v>
+        <v>130205932</v>
       </c>
       <c r="B4" t="n">
-        <v>57042</v>
+        <v>79828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555987</v>
+        <v>555963</v>
       </c>
       <c r="R4" t="n">
-        <v>6440734</v>
+        <v>6440548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,60 +967,56 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130206069</v>
+        <v>130206032</v>
       </c>
       <c r="B5" t="n">
-        <v>57042</v>
+        <v>79828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1029,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556351</v>
+        <v>556137</v>
       </c>
       <c r="R5" t="n">
-        <v>6440550</v>
+        <v>6440697</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,6 +1068,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1084,39 +1080,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130206062</v>
+        <v>130192475</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>57042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,7 +1120,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1134,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556289</v>
+        <v>556371</v>
       </c>
       <c r="R6" t="n">
-        <v>6440643</v>
+        <v>6440485</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,22 +1180,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130192966</v>
+        <v>130207870</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>57042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1207,43 +1203,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556440</v>
+        <v>555987</v>
       </c>
       <c r="R7" t="n">
-        <v>6440510</v>
+        <v>6440734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,29 +1283,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192475</v>
+        <v>130192966</v>
       </c>
       <c r="B8" t="n">
-        <v>57042</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1314,29 +1312,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1346,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556371</v>
+        <v>556440</v>
       </c>
       <c r="R8" t="n">
-        <v>6440485</v>
+        <v>6440510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,6 +1389,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1516,7 +1516,7 @@
         <v>130205883</v>
       </c>
       <c r="B10" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>130206011</v>
       </c>
       <c r="B11" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1916,7 +1916,7 @@
         <v>130206042</v>
       </c>
       <c r="B14" t="n">
-        <v>93032</v>
+        <v>93033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
         <v>130205999</v>
       </c>
       <c r="B15" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2522,7 +2522,7 @@
         <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130181235</v>
+        <v>130191022</v>
       </c>
       <c r="B23" t="n">
-        <v>93040</v>
+        <v>57042</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,34 +2821,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555982</v>
+        <v>556359</v>
       </c>
       <c r="R23" t="n">
-        <v>6440530</v>
+        <v>6440535</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2907,10 +2915,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130191022</v>
+        <v>130188529</v>
       </c>
       <c r="B24" t="n">
-        <v>57042</v>
+        <v>8451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2918,29 +2926,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2950,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556359</v>
+        <v>556326</v>
       </c>
       <c r="R24" t="n">
-        <v>6440535</v>
+        <v>6440589</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,6 +3003,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3012,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130188529</v>
+        <v>130181235</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>93041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3023,43 +3033,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556326</v>
+        <v>555982</v>
       </c>
       <c r="R25" t="n">
-        <v>6440589</v>
+        <v>6440530</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,7 +3101,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3119,10 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130184293</v>
+        <v>130206076</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>93041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,34 +3130,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556081</v>
+        <v>556535</v>
       </c>
       <c r="R26" t="n">
-        <v>6440690</v>
+        <v>6440485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3198,55 +3201,61 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206076</v>
+        <v>130206002</v>
       </c>
       <c r="B27" t="n">
-        <v>93040</v>
+        <v>57849</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3254,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556535</v>
+        <v>556108</v>
       </c>
       <c r="R27" t="n">
-        <v>6440485</v>
+        <v>6440698</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3298,7 +3307,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3310,14 +3318,14 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130206002</v>
+        <v>130205958</v>
       </c>
       <c r="B28" t="n">
         <v>57849</v>
@@ -3360,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556108</v>
+        <v>556008</v>
       </c>
       <c r="R28" t="n">
-        <v>6440698</v>
+        <v>6440596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3415,60 +3423,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130205958</v>
+        <v>130184293</v>
       </c>
       <c r="B29" t="n">
-        <v>57849</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556008</v>
+        <v>556081</v>
       </c>
       <c r="R29" t="n">
-        <v>6440596</v>
+        <v>6440690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,61 +3515,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130206072</v>
+        <v>130181118</v>
       </c>
       <c r="B30" t="n">
-        <v>96439</v>
+        <v>79828</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556413</v>
+        <v>555982</v>
       </c>
       <c r="R30" t="n">
-        <v>6440503</v>
+        <v>6440530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,64 +3606,67 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130181118</v>
+        <v>130206072</v>
       </c>
       <c r="B31" t="n">
-        <v>79828</v>
+        <v>96440</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555982</v>
+        <v>556413</v>
       </c>
       <c r="R31" t="n">
-        <v>6440530</v>
+        <v>6440503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,71 +3707,64 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130193838</v>
+        <v>130191846</v>
       </c>
       <c r="B32" t="n">
-        <v>57042</v>
+        <v>78875</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556003</v>
+        <v>556374</v>
       </c>
       <c r="R32" t="n">
-        <v>6440837</v>
+        <v>6440510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3831,10 +3823,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B33" t="n">
-        <v>78875</v>
+        <v>79828</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3842,34 +3834,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R33" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,55 +3905,61 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130206052</v>
+        <v>130193838</v>
       </c>
       <c r="B34" t="n">
-        <v>79828</v>
+        <v>57042</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3966,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556177</v>
+        <v>556003</v>
       </c>
       <c r="R34" t="n">
-        <v>6440700</v>
+        <v>6440837</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4010,19 +4011,18 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130206069</v>
+        <v>130192966</v>
       </c>
       <c r="B2" t="n">
-        <v>57042</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556351</v>
+        <v>556440</v>
       </c>
       <c r="R2" t="n">
-        <v>6440550</v>
+        <v>6440510</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,18 +763,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -783,7 +785,7 @@
         <v>130206062</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,55 +880,64 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130205932</v>
+        <v>130207870</v>
       </c>
       <c r="B4" t="n">
-        <v>79828</v>
+        <v>57044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555963</v>
+        <v>555987</v>
       </c>
       <c r="R4" t="n">
-        <v>6440548</v>
+        <v>6440734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,56 +978,60 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130206032</v>
+        <v>130206069</v>
       </c>
       <c r="B5" t="n">
-        <v>79828</v>
+        <v>57044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1024,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556137</v>
+        <v>556351</v>
       </c>
       <c r="R5" t="n">
-        <v>6440697</v>
+        <v>6440550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1083,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1080,7 +1094,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1090,7 +1104,7 @@
         <v>130192475</v>
       </c>
       <c r="B6" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,57 +1206,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130207870</v>
+        <v>130205932</v>
       </c>
       <c r="B7" t="n">
-        <v>57042</v>
+        <v>79830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555987</v>
+        <v>555963</v>
       </c>
       <c r="R7" t="n">
-        <v>6440734</v>
+        <v>6440548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,61 +1288,56 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192966</v>
+        <v>130206032</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556440</v>
+        <v>556137</v>
       </c>
       <c r="R8" t="n">
-        <v>6440510</v>
+        <v>6440697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,12 +1396,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1411,7 +1411,7 @@
         <v>130188519</v>
       </c>
       <c r="B9" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>130205883</v>
       </c>
       <c r="B10" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>130206011</v>
       </c>
       <c r="B11" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1718,7 +1718,7 @@
         <v>130184588</v>
       </c>
       <c r="B12" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>130206073</v>
       </c>
       <c r="B13" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130206042</v>
+        <v>130205999</v>
       </c>
       <c r="B14" t="n">
-        <v>93033</v>
+        <v>91782</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556130</v>
+        <v>556087</v>
       </c>
       <c r="R14" t="n">
-        <v>6440718</v>
+        <v>6440692</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130205999</v>
+        <v>130206042</v>
       </c>
       <c r="B15" t="n">
-        <v>91780</v>
+        <v>93035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556087</v>
+        <v>556130</v>
       </c>
       <c r="R15" t="n">
-        <v>6440692</v>
+        <v>6440718</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2118,7 +2118,7 @@
         <v>130205992</v>
       </c>
       <c r="B16" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2219,7 +2219,7 @@
         <v>130184338</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>130184193</v>
       </c>
       <c r="B18" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>130206066</v>
       </c>
       <c r="B19" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2522,7 +2522,7 @@
         <v>130184275</v>
       </c>
       <c r="B20" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>130188670</v>
       </c>
       <c r="B21" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>130186120</v>
       </c>
       <c r="B22" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2810,10 +2810,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130191022</v>
+        <v>130181235</v>
       </c>
       <c r="B23" t="n">
-        <v>57042</v>
+        <v>93043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2821,42 +2821,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>556359</v>
+        <v>555982</v>
       </c>
       <c r="R23" t="n">
-        <v>6440535</v>
+        <v>6440530</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2915,10 +2907,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130188529</v>
+        <v>130191022</v>
       </c>
       <c r="B24" t="n">
-        <v>8451</v>
+        <v>57044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,30 +2918,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -2959,10 +2950,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556326</v>
+        <v>556359</v>
       </c>
       <c r="R24" t="n">
-        <v>6440589</v>
+        <v>6440535</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,7 +2994,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3022,10 +3012,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130181235</v>
+        <v>130188529</v>
       </c>
       <c r="B25" t="n">
-        <v>93041</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,34 +3023,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>555982</v>
+        <v>556326</v>
       </c>
       <c r="R25" t="n">
-        <v>6440530</v>
+        <v>6440589</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,6 +3100,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>130206076</v>
       </c>
       <c r="B26" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,53 +3220,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130206002</v>
+        <v>130184293</v>
       </c>
       <c r="B27" t="n">
-        <v>57849</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556108</v>
+        <v>556081</v>
       </c>
       <c r="R27" t="n">
-        <v>6440698</v>
+        <v>6440690</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3313,22 +3305,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130205958</v>
+        <v>130206002</v>
       </c>
       <c r="B28" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556008</v>
+        <v>556108</v>
       </c>
       <c r="R28" t="n">
-        <v>6440596</v>
+        <v>6440698</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,52 +3415,60 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130184293</v>
+        <v>130205958</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57851</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556081</v>
+        <v>556008</v>
       </c>
       <c r="R29" t="n">
-        <v>6440690</v>
+        <v>6440596</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,57 +3515,61 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130181118</v>
+        <v>130206072</v>
       </c>
       <c r="B30" t="n">
-        <v>79828</v>
+        <v>96442</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555982</v>
+        <v>556413</v>
       </c>
       <c r="R30" t="n">
-        <v>6440530</v>
+        <v>6440503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,67 +3610,64 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130206072</v>
+        <v>130181118</v>
       </c>
       <c r="B31" t="n">
-        <v>96440</v>
+        <v>79830</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556413</v>
+        <v>555982</v>
       </c>
       <c r="R31" t="n">
-        <v>6440503</v>
+        <v>6440530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,29 +3708,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B32" t="n">
-        <v>78875</v>
+        <v>79830</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,34 +3737,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R32" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3805,55 +3808,61 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130206052</v>
+        <v>130193838</v>
       </c>
       <c r="B33" t="n">
-        <v>79828</v>
+        <v>57044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3861,10 +3870,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556177</v>
+        <v>556003</v>
       </c>
       <c r="R33" t="n">
-        <v>6440700</v>
+        <v>6440837</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,72 +3914,63 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130193838</v>
+        <v>130191846</v>
       </c>
       <c r="B34" t="n">
-        <v>57042</v>
+        <v>78877</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556003</v>
+        <v>556374</v>
       </c>
       <c r="R34" t="n">
-        <v>6440837</v>
+        <v>6440510</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4032,7 +4032,7 @@
         <v>130193547</v>
       </c>
       <c r="B35" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>130206059</v>
       </c>
       <c r="B36" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4238,7 +4238,7 @@
         <v>130206077</v>
       </c>
       <c r="B37" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>130193214</v>
       </c>
       <c r="B38" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -675,41 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192966</v>
+        <v>130206062</v>
       </c>
       <c r="B2" t="n">
-        <v>8451</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556440</v>
+        <v>556289</v>
       </c>
       <c r="R2" t="n">
-        <v>6440510</v>
+        <v>6440643</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,72 +762,75 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130206062</v>
+        <v>130207870</v>
       </c>
       <c r="B3" t="n">
-        <v>57851</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556289</v>
+        <v>555987</v>
       </c>
       <c r="R3" t="n">
-        <v>6440643</v>
+        <v>6440734</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +877,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130207870</v>
+        <v>130206069</v>
       </c>
       <c r="B4" t="n">
         <v>57044</v>
@@ -915,29 +917,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555987</v>
+        <v>556351</v>
       </c>
       <c r="R4" t="n">
-        <v>6440734</v>
+        <v>6440550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,19 +982,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130206069</v>
+        <v>130192475</v>
       </c>
       <c r="B5" t="n">
         <v>57044</v>
@@ -1039,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556351</v>
+        <v>556371</v>
       </c>
       <c r="R5" t="n">
-        <v>6440550</v>
+        <v>6440485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,54 +1087,49 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130192475</v>
+        <v>130205932</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>79830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1144,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556371</v>
+        <v>555963</v>
       </c>
       <c r="R6" t="n">
-        <v>6440485</v>
+        <v>6440548</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,25 +1181,26 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130205932</v>
+        <v>130206032</v>
       </c>
       <c r="B7" t="n">
         <v>79830</v>
@@ -1244,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555963</v>
+        <v>556137</v>
       </c>
       <c r="R7" t="n">
-        <v>6440548</v>
+        <v>6440697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,44 +1294,50 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130206032</v>
+        <v>130192966</v>
       </c>
       <c r="B8" t="n">
-        <v>79830</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556137</v>
+        <v>556440</v>
       </c>
       <c r="R8" t="n">
-        <v>6440697</v>
+        <v>6440510</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,12 +1396,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130205999</v>
+        <v>130206042</v>
       </c>
       <c r="B14" t="n">
-        <v>91782</v>
+        <v>93039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556087</v>
+        <v>556130</v>
       </c>
       <c r="R14" t="n">
-        <v>6440692</v>
+        <v>6440718</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130206042</v>
+        <v>130205999</v>
       </c>
       <c r="B15" t="n">
-        <v>93035</v>
+        <v>91782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556130</v>
+        <v>556087</v>
       </c>
       <c r="R15" t="n">
-        <v>6440718</v>
+        <v>6440692</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2813,7 +2813,7 @@
         <v>130181235</v>
       </c>
       <c r="B23" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>130206076</v>
       </c>
       <c r="B26" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3220,45 +3220,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130184293</v>
+        <v>130205958</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>57851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556081</v>
+        <v>556008</v>
       </c>
       <c r="R27" t="n">
-        <v>6440690</v>
+        <v>6440596</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3305,12 +3313,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3415,60 +3423,52 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130205958</v>
+        <v>130184293</v>
       </c>
       <c r="B29" t="n">
-        <v>57851</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556008</v>
+        <v>556081</v>
       </c>
       <c r="R29" t="n">
-        <v>6440596</v>
+        <v>6440690</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,61 +3515,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130206072</v>
+        <v>130181118</v>
       </c>
       <c r="B30" t="n">
-        <v>96442</v>
+        <v>79830</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>556413</v>
+        <v>555982</v>
       </c>
       <c r="R30" t="n">
-        <v>6440503</v>
+        <v>6440530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3610,64 +3606,67 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130181118</v>
+        <v>130206072</v>
       </c>
       <c r="B31" t="n">
-        <v>79830</v>
+        <v>96446</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>555982</v>
+        <v>556413</v>
       </c>
       <c r="R31" t="n">
-        <v>6440530</v>
+        <v>6440503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3708,28 +3707,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130206052</v>
+        <v>130191846</v>
       </c>
       <c r="B32" t="n">
-        <v>79830</v>
+        <v>78877</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,37 +3737,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556177</v>
+        <v>556374</v>
       </c>
       <c r="R32" t="n">
-        <v>6440700</v>
+        <v>6440510</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3808,19 +3805,18 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3932,10 +3928,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130191846</v>
+        <v>130206052</v>
       </c>
       <c r="B34" t="n">
-        <v>78877</v>
+        <v>79830</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3943,34 +3939,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556374</v>
+        <v>556177</v>
       </c>
       <c r="R34" t="n">
-        <v>6440510</v>
+        <v>6440700</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4011,18 +4010,19 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130206062</v>
+        <v>130191846</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556289</v>
+        <v>556374</v>
       </c>
       <c r="R2" t="n">
-        <v>6440643</v>
+        <v>6440510</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130207870</v>
+        <v>130206054</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,46 +783,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grankärren, Vilebo, Ög</t>
+          <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555987</v>
+        <v>556240</v>
       </c>
       <c r="R3" t="n">
-        <v>6440734</v>
+        <v>6440650</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,28 +855,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Emil Ideskär</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130206069</v>
+        <v>130206072</v>
       </c>
       <c r="B4" t="n">
-        <v>57044</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,31 +885,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556351</v>
+        <v>556413</v>
       </c>
       <c r="R4" t="n">
-        <v>6440550</v>
+        <v>6440503</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +957,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,42 +976,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130192475</v>
+        <v>130206042</v>
       </c>
       <c r="B5" t="n">
-        <v>57044</v>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556371</v>
+        <v>556130</v>
       </c>
       <c r="R5" t="n">
-        <v>6440485</v>
+        <v>6440718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,28 +1058,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130205932</v>
+        <v>130181235</v>
       </c>
       <c r="B6" t="n">
-        <v>79830</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,37 +1088,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555963</v>
+        <v>555982</v>
       </c>
       <c r="R6" t="n">
-        <v>6440548</v>
+        <v>6440530</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,29 +1156,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130206032</v>
+        <v>130206076</v>
       </c>
       <c r="B7" t="n">
-        <v>79830</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1185,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1212,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>556137</v>
+        <v>556535</v>
       </c>
       <c r="R7" t="n">
-        <v>6440697</v>
+        <v>6440485</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,61 +1268,52 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192966</v>
+        <v>130184275</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>556440</v>
+        <v>556081</v>
       </c>
       <c r="R8" t="n">
-        <v>6440510</v>
+        <v>6440690</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1354,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1401,17 +1365,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130188519</v>
+        <v>130205883</v>
       </c>
       <c r="B9" t="n">
-        <v>57851</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,31 +1383,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1451,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>556309</v>
+        <v>556006</v>
       </c>
       <c r="R9" t="n">
-        <v>6440596</v>
+        <v>6440538</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,28 +1454,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130205883</v>
+        <v>130205999</v>
       </c>
       <c r="B10" t="n">
-        <v>91782</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556006</v>
+        <v>556087</v>
       </c>
       <c r="R10" t="n">
-        <v>6440538</v>
+        <v>6440692</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1567,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1617,7 +1577,7 @@
         <v>130206011</v>
       </c>
       <c r="B11" t="n">
-        <v>91725</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,17 +1668,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130184588</v>
+        <v>130181118</v>
       </c>
       <c r="B12" t="n">
-        <v>79830</v>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>556081</v>
+        <v>555982</v>
       </c>
       <c r="R12" t="n">
-        <v>6440690</v>
+        <v>6440530</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130206073</v>
+        <v>130184193</v>
       </c>
       <c r="B13" t="n">
-        <v>79830</v>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1841,19 +1801,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>556420</v>
+        <v>556010</v>
       </c>
       <c r="R13" t="n">
-        <v>6440506</v>
+        <v>6440623</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,29 +1851,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130206042</v>
+        <v>130184588</v>
       </c>
       <c r="B14" t="n">
-        <v>93039</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,37 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>556130</v>
+        <v>556081</v>
       </c>
       <c r="R14" t="n">
-        <v>6440718</v>
+        <v>6440690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,29 +1948,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130205999</v>
+        <v>130186120</v>
       </c>
       <c r="B15" t="n">
-        <v>91782</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2025,37 +1977,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>556087</v>
+        <v>556179</v>
       </c>
       <c r="R15" t="n">
-        <v>6440692</v>
+        <v>6440716</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,29 +2045,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130205992</v>
+        <v>130188670</v>
       </c>
       <c r="B16" t="n">
-        <v>79830</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2144,19 +2092,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>555991</v>
+        <v>556335</v>
       </c>
       <c r="R16" t="n">
-        <v>6440609</v>
+        <v>6440570</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,29 +2142,28 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130184338</v>
+        <v>130193214</v>
       </c>
       <c r="B17" t="n">
-        <v>57851</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2227,42 +2171,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>556081</v>
+        <v>556550</v>
       </c>
       <c r="R17" t="n">
-        <v>6440690</v>
+        <v>6440532</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,10 +2257,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130184193</v>
+        <v>130205932</v>
       </c>
       <c r="B18" t="n">
-        <v>79830</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2350,16 +2286,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>556010</v>
+        <v>555963</v>
       </c>
       <c r="R18" t="n">
-        <v>6440623</v>
+        <v>6440548</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,28 +2339,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130206066</v>
+        <v>130205992</v>
       </c>
       <c r="B19" t="n">
-        <v>79830</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2456,10 +2396,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>556348</v>
+        <v>555991</v>
       </c>
       <c r="R19" t="n">
-        <v>6440509</v>
+        <v>6440609</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,17 +2452,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130184275</v>
+        <v>130206032</v>
       </c>
       <c r="B20" t="n">
-        <v>91782</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2530,34 +2470,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>556081</v>
+        <v>556137</v>
       </c>
       <c r="R20" t="n">
-        <v>6440690</v>
+        <v>6440697</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,28 +2541,29 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130188670</v>
+        <v>130206052</v>
       </c>
       <c r="B21" t="n">
-        <v>79830</v>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,16 +2589,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>556335</v>
+        <v>556177</v>
       </c>
       <c r="R21" t="n">
-        <v>6440570</v>
+        <v>6440700</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2695,28 +2642,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130186120</v>
+        <v>130206059</v>
       </c>
       <c r="B22" t="n">
-        <v>79830</v>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,16 +2690,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>556179</v>
+        <v>556285</v>
       </c>
       <c r="R22" t="n">
-        <v>6440716</v>
+        <v>6440650</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2792,63 +2743,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130181235</v>
+        <v>130206066</v>
       </c>
       <c r="B23" t="n">
-        <v>93047</v>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>555982</v>
+        <v>556348</v>
       </c>
       <c r="R23" t="n">
-        <v>6440530</v>
+        <v>6440509</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2889,60 +2844,56 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130191022</v>
+        <v>130206073</v>
       </c>
       <c r="B24" t="n">
-        <v>57044</v>
+        <v>79946</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2950,10 +2901,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>556359</v>
+        <v>556420</v>
       </c>
       <c r="R24" t="n">
-        <v>6440535</v>
+        <v>6440506</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2994,61 +2945,56 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130188529</v>
+        <v>130206077</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3056,10 +3002,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>556326</v>
+        <v>556524</v>
       </c>
       <c r="R25" t="n">
-        <v>6440589</v>
+        <v>6440529</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3107,22 +3053,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130206076</v>
+        <v>130184338</v>
       </c>
       <c r="B26" t="n">
-        <v>93047</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,26 +3076,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3157,10 +3108,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>556535</v>
+        <v>556081</v>
       </c>
       <c r="R26" t="n">
-        <v>6440485</v>
+        <v>6440690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3201,33 +3152,32 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130205958</v>
+        <v>130188519</v>
       </c>
       <c r="B27" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3253,7 +3203,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3263,7 +3213,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>556008</v>
+        <v>556309</v>
       </c>
       <c r="R27" t="n">
         <v>6440596</v>
@@ -3313,26 +3263,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130206002</v>
+        <v>130205958</v>
       </c>
       <c r="B28" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3368,10 +3318,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>556108</v>
+        <v>556008</v>
       </c>
       <c r="R28" t="n">
-        <v>6440698</v>
+        <v>6440596</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,17 +3373,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Gabriel Johansson, Lena Lundin Johansson, Hasse Andersson, Emma Nordenberg, Andreas Mathisen, Steve Daurer, Lisa Winberg, Minna Axert</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130184293</v>
+        <v>130206002</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3441,34 +3391,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>556081</v>
+        <v>556108</v>
       </c>
       <c r="R29" t="n">
-        <v>6440690</v>
+        <v>6440698</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,57 +3473,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130181118</v>
+        <v>130206062</v>
       </c>
       <c r="B30" t="n">
-        <v>79830</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>555982</v>
+        <v>556289</v>
       </c>
       <c r="R30" t="n">
-        <v>6440530</v>
+        <v>6440643</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3612,22 +3578,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130206072</v>
+        <v>130191022</v>
       </c>
       <c r="B31" t="n">
-        <v>96446</v>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3635,27 +3601,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3663,10 +3633,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>556413</v>
+        <v>556359</v>
       </c>
       <c r="R31" t="n">
-        <v>6440503</v>
+        <v>6440535</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3707,64 +3677,71 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130191846</v>
+        <v>130192475</v>
       </c>
       <c r="B32" t="n">
-        <v>78877</v>
+        <v>57141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>556374</v>
+        <v>556371</v>
       </c>
       <c r="R32" t="n">
-        <v>6440510</v>
+        <v>6440485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3816,17 +3793,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Lisa Winberg, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130193838</v>
+        <v>130193547</v>
       </c>
       <c r="B33" t="n">
-        <v>57044</v>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3856,7 +3833,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3866,10 +3843,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>556003</v>
+        <v>556301</v>
       </c>
       <c r="R33" t="n">
-        <v>6440837</v>
+        <v>6440760</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,37 +3905,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130206052</v>
+        <v>130193838</v>
       </c>
       <c r="B34" t="n">
-        <v>79830</v>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3966,10 +3948,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>556177</v>
+        <v>556003</v>
       </c>
       <c r="R34" t="n">
-        <v>6440700</v>
+        <v>6440837</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4010,29 +3992,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130193547</v>
+        <v>130206069</v>
       </c>
       <c r="B35" t="n">
-        <v>57044</v>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4072,10 +4053,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>556301</v>
+        <v>556351</v>
       </c>
       <c r="R35" t="n">
-        <v>6440760</v>
+        <v>6440550</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4122,60 +4103,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Gabriel Johansson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
+          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130206059</v>
+        <v>130207870</v>
       </c>
       <c r="B36" t="n">
-        <v>79830</v>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Grankärren, Ög</t>
+          <t>Grankärren, Vilebo, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>556285</v>
+        <v>555987</v>
       </c>
       <c r="R36" t="n">
-        <v>6440650</v>
+        <v>6440734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4216,67 +4206,63 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emil Ideskär</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Steve Daurer, Andreas Mathisen, Emma Nordenberg, Lena Lundin Johansson, Hasse Andersson, Lisa Winberg, Minna Axert, Gabriel Johansson</t>
+          <t>Steve Daurer, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130206077</v>
+        <v>130184293</v>
       </c>
       <c r="B37" t="n">
-        <v>79830</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>556524</v>
+        <v>556081</v>
       </c>
       <c r="R37" t="n">
-        <v>6440529</v>
+        <v>6440690</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4317,64 +4303,72 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gabriel Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gabriel Johansson, Minna Axert, Lisa Winberg, Hasse Andersson, Lena Lundin Johansson, Emma Nordenberg, Andreas Mathisen, Steve Daurer</t>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Lisa Winberg, Minna Axert, Emil Ideskär</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130193214</v>
+        <v>130188529</v>
       </c>
       <c r="B38" t="n">
-        <v>79830</v>
+        <v>8455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Grankärren, Ög</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>556550</v>
+        <v>556326</v>
       </c>
       <c r="R38" t="n">
-        <v>6440532</v>
+        <v>6440589</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4415,6 +4409,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4430,6 +4425,113 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130192966</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grankärren, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>556440</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6440510</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kättilstad</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Gabriel Johansson, Hasse Andersson, Andreas Mathisen, Lena Lundin Johansson, Steve Daurer, Minna Axert, Emil Ideskär, Lisa Winberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54477-2025 artfynd.xlsx
+++ b/artfynd/A 54477-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206054</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206072</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206042</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181235</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206076</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184275</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130205883</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130205999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206011</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130181118</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184193</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184588</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130186120</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130188670</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130193214</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2355,6 +2440,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130205932</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2456,6 +2546,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130205992</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2557,6 +2652,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206032</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2658,6 +2758,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206052</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2759,6 +2864,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206059</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2860,6 +2970,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206066</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2961,6 +3076,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206073</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3062,6 +3182,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206077</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3167,6 +3292,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184338</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3272,6 +3402,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130188519</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3377,6 +3512,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130205958</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3482,6 +3622,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206002</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3587,6 +3732,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206062</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3692,6 +3842,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191022</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3797,6 +3952,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192475</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3902,6 +4062,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130193547</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4007,6 +4172,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130193838</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4112,6 +4282,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130206069</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4221,6 +4396,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130207870</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4318,6 +4498,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184293</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4425,6 +4610,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130188529</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4532,8 +4722,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192966</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>